--- a/electrician_forms/005_underground_insulation_resistance_testing_form--electrician_forms.xlsx
+++ b/electrician_forms/005_underground_insulation_resistance_testing_form--electrician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'air',_'label':_'air'}</t>
+          <t>air</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'air', 'label': 'Air'}</t>
+          <t>Air</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'cable',_'label':_'cable'}</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'cable', 'label': 'Cable'}</t>
+          <t>Cable</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'pipe',_'label':_'pipe'}</t>
+          <t>pipe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'pipe', 'label': 'Pipe'}</t>
+          <t>Pipe</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'wire',_'label':_'wire'}</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'wire', 'label': 'Wire'}</t>
+          <t>Wire</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'ohm',_'label':_'ohm'}</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'ohm', 'label': 'Ohm'}</t>
+          <t>Ohm</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'kohm',_'label':_'kohm'}</t>
+          <t>kohm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'kohm', 'label': 'KOhm'}</t>
+          <t>KOhm</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'mohm',_'label':_'mohm'}</t>
+          <t>mohm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'mohm', 'label': 'MOhm'}</t>
+          <t>MOhm</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'air',_'label':_'air'}</t>
+          <t>air</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'air', 'label': 'Air'}</t>
+          <t>Air</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cable',_'label':_'cable'}</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'cable', 'label': 'Cable'}</t>
+          <t>Cable</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'pipe',_'label':_'pipe'}</t>
+          <t>pipe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'pipe', 'label': 'Pipe'}</t>
+          <t>Pipe</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'wire',_'label':_'wire'}</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'wire', 'label': 'Wire'}</t>
+          <t>Wire</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'ohm',_'label':_'ohm'}</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'ohm', 'label': 'Ohm'}</t>
+          <t>Ohm</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'kohm',_'label':_'kohm'}</t>
+          <t>kohm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'kohm', 'label': 'KOhm'}</t>
+          <t>KOhm</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'mohm',_'label':_'mohm'}</t>
+          <t>mohm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'mohm', 'label': 'MOhm'}</t>
+          <t>MOhm</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'room',_'label':_'room'}</t>
+          <t>room</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'room', 'label': 'Room'}</t>
+          <t>Room</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'ambient',_'label':_'ambient'}</t>
+          <t>ambient</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'ambient', 'label': 'Ambient'}</t>
+          <t>Ambient</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'unknown',_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'unknown', 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'jimmy',_'label':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'jimmy', 'label': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'jane',_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'jane', 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'jimmy',_'label':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'jimmy', 'label': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'jane',_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'jane', 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'true',_'label':_'true'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'true', 'label': 'True'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'false',_'label':_'false'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'false', 'label': 'False'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
